--- a/Excel+LAB+1+Dataset_Dmart(1).xlsx
+++ b/Excel+LAB+1+Dataset_Dmart(1).xlsx
@@ -7325,7 +7325,7 @@
       </c>
       <c r="AI16" s="13">
         <f ca="1">NOW()</f>
-        <v>46247.4865393518</v>
+        <v>46252.5413310185</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1" spans="1:35">
@@ -7446,7 +7446,7 @@
       </c>
       <c r="AI17" s="14">
         <f ca="1">TODAY()</f>
-        <v>46247</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1" spans="1:35">
